--- a/Result/checksun_type/驅動IC.xlsx
+++ b/Result/checksun_type/驅動IC.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>44.41</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>43.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>90702033.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>105746633.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>105746633</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>142323916.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>283181158.2</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>283181158.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-35659135.80271852</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>90702033</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>90702033.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>44.26000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>87525673.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>110801500.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>110801500.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>189373875.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>283370598.82</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>283370598.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-35489764.01778525</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>87525673</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>87525673.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>44.24999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>43.64</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>43.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>128580046.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>123016262.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>123016262.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>222414981.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>283171455.62</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>283171455.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-33639988.4672454</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>128580046</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>128580046.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>44.57</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>45.41</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>43.59</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>43.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>113653630.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>135354845.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>135354845.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>226837017.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>282518805.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>282518805.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-34194706.62835827</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>113653630</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>113653630.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.91</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>43.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>108271783.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>145615587.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>145615587.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>232423142.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>281761516.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>281761516.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-32166662.7646496</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>108271783</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>108271783.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>45.24</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>43.46</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>115976369.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>178901199.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>178901199.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>246879753.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>282984175.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>282984175.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-27544021.3963283</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>115976369</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>115976369.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>45.97</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>43.39</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>43.39</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>148599483.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>267946251.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>267946251.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>246572505.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>282049366.78</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>282049366.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-20782024.32028615</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>148599483</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>148599483.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>46.44</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>43.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>190272964.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>321813700.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>321813700.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>247253736.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>280836529.52</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>280836529.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-13875146.98593</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>190272964</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>190272964.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>46.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>43.23</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>43.23</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>164957337.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>318319189.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>318319189.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>250999781.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>282811790.16</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>282811790.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-7977654.223066568</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>164957337</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>164957337.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>46.52</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>45.31</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>43.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>274699843.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>319230697.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>319230697.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>284091819.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>289666457.52</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>289666457.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>3444640.267562151</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>274699843</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>274699843.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>46.35</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>45.14</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>43.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>43.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>561201630.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>314858307.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>314858307.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>295191794.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>297124608.34</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>297124608.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>7881055.316047311</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>561201630</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>561201630.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>51.94</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>55.43</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>55.85</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>55.85</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>171410.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>212080.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>212080</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>212554.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>176745.28</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>176745.28</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>3500.251280392607</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>171410</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>171410.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>51.77999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>55.77</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>55.88</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>55.88</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>169863.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>232057.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>232057</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>206159.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>175562.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>175562.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>7544.847136975062</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>169863</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>169863.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>51.67999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>56.04</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>55.93</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>55.93</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>225485.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>263973.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>263973.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>197652.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>174202.52</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>174202.52</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>13219.13239148661</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>225485</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>225485.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>52.12</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>55.99</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>269413.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>276210.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>276210.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>181567.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>172395.86</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>172395.86</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>14893.64231252146</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>269413</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>269413.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>56.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>56.06</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>224229.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>241969.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>241969.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>168691.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>171186.76</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>171186.76</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>12047.31211712403</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>224229</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>224229.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>54.06</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>56.89</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>56.08</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>56.08</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>271295.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>213028.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>213028.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>158228.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>168027.38</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>168027.38</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>12392.00783380185</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>271295</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>271295.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>55.14</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>57.26</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>56.13</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>56.13</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>329447.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>180262.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>180262.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>147004.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>164331.36</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>164331.36</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>7399.072863562964</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>329447</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>329447.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>56.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>57.58</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>286670.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>131330.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>131330.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>140339.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>158954.44</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>158954.44</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-6228.515410477004</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>286670</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>286670.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>56.65999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>57.76</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>56.16</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>56.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>98207.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>86924.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>86924.60000000001</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>154222.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>154174.54</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>154174.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-20890.8016801599</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>98207</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>98207.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>56.64</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>57.79</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>56.1</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>56.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>79523.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>95414.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>95414.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>170945.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>153254.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>153254.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-20898.36057684405</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>79523</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>79523.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>56.77999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>57.76</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>56.03</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>56.03</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>107464.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>103428.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>103428.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>174988.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>153137.02</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>153137.02</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-18160.9318372198</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>107464</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>107464.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>51.21</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>53.08</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>57.02</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>57.02</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>18202.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>9349.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>9349.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>7989.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>13460.24</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>13460.24</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>500.6753961315808</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>18202</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>18202.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>50.71</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>53.27</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>57.18</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>57.18</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>17036.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6987.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6987.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>6636.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>14299.4</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>14299.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-325.7147088748216</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>17036</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>17036.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>50.42999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>53.55</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>57.46</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2323.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4899.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>4899.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>6022.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>15417.3</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>15417.3</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1369.710762138438</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2323</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2323.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>50.73</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>53.94</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>57.69</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3535.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>5598.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>5598</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>6458.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>15662.04</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>15662.04</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1235.822596724375</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3535</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3535.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>51.26000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>54.33</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>57.9</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>5651.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>6317.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>6317.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>7375.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>15916.1</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>15916.1</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1130.274410535557</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>5651</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>5651.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>51.94</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>58.1</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>6391.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>6629.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>6629.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>7233.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>16143.36</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>16143.36</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1165.838629889547</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>6391</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>6391.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>52.62</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>55.11</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>58.29</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>6596.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>6285.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>6285.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>7319.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>16730.98</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>16730.98</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1254.293277899191</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>6596</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>6596.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>53.27999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>55.51</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>58.53</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>58.53</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>5817.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>7145.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>7145.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>7601.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>17385.02</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>17385.02</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1357.825157987996</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>5817</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>5817.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>53.73999999999999</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>55.81</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>58.76</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>7133.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>7319.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>7319.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>7839.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>19212.02</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>19212.02</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1373.769802472432</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>7133</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>7133.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>53.96</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>56.14</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>59.1</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>7209.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>8433.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>8433</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>7485.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>23000.42</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>23000.42</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1488.484658790469</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>7209</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>7209.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>53.86</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>56.38</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>59.37</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>4672.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>7837.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>7837.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>8182.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>23577.74</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>23577.74</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1607.345715716578</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>4672</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15259,11 +15061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>2459</t>
@@ -15445,41 +15243,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr">
         <is>
           <t>0</t>
@@ -15500,20 +15294,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>0</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
